--- a/outputs/monitor_xlsx/20260209.xlsx
+++ b/outputs/monitor_xlsx/20260209.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1193,12 +1191,7 @@
       <c r="N4" t="n">
         <v>2.35</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1236,12 +1229,7 @@
       <c r="M5" t="n">
         <v>-29524</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1291,12 +1279,7 @@
       <c r="N6" t="n">
         <v>-0.42</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1349,12 +1332,7 @@
       <c r="N7" t="n">
         <v>-2.61</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1407,12 +1385,7 @@
       <c r="N8" t="n">
         <v>-0.17</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1465,12 +1438,7 @@
       <c r="N9" t="n">
         <v>2.02</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1523,12 +1491,7 @@
       <c r="N10" t="n">
         <v>1.36</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1581,12 +1544,7 @@
       <c r="N11" t="n">
         <v>8.84</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1639,12 +1597,7 @@
       <c r="N12" t="n">
         <v>1.36</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1697,12 +1650,7 @@
       <c r="N13" t="n">
         <v>-2.73</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1755,12 +1703,7 @@
       <c r="N14" t="n">
         <v>4.52</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1813,12 +1756,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1871,12 +1809,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1926,12 +1859,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1984,12 +1912,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2042,12 +1965,7 @@
       <c r="N19" t="n">
         <v>1.03</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2100,11 +2018,6 @@
       <c r="N20" t="n">
         <v>-2.29</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2153,11 +2066,6 @@
       <c r="N21" t="n">
         <v>0.72</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2206,11 +2114,6 @@
       <c r="N22" t="n">
         <v>-9.49</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2259,11 +2162,6 @@
       <c r="N23" t="n">
         <v>10.69</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2312,11 +2210,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2365,11 +2258,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2418,11 +2306,6 @@
       <c r="N26" t="n">
         <v>2.52</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2470,11 +2353,6 @@
       </c>
       <c r="N27" t="n">
         <v>7.65</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260209.xlsx
+++ b/outputs/monitor_xlsx/20260209.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,44 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>73.95</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>2.85</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>122340</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>36795</v>
       </c>
-      <c r="G4" t="n">
-        <v>-171136</v>
-      </c>
       <c r="H4" t="n">
+        <v>-55232</v>
+      </c>
+      <c r="I4" t="n">
         <v>2200</v>
       </c>
-      <c r="I4" t="n">
-        <v>2205</v>
-      </c>
       <c r="J4" t="n">
+        <v>6400</v>
+      </c>
+      <c r="K4" t="n">
         <v>11405</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7238</v>
       </c>
-      <c r="L4" t="n">
-        <v>38897</v>
-      </c>
       <c r="M4" t="n">
+        <v>38221</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4038144</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.35</v>
+      <c r="O4" t="n">
+        <v>2.26</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1246,38 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>945</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>3.85</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="7" t="n">
         <v>2311</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>183</v>
       </c>
-      <c r="G6" t="n">
-        <v>-373</v>
+      <c r="H6" t="n">
+        <v>-882</v>
       </c>
       <c r="I6" t="n">
-        <v>-197</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K6" t="n">
         <v>28</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2866</v>
       </c>
-      <c r="L6" t="n">
-        <v>13985</v>
-      </c>
       <c r="M6" t="n">
+        <v>14259</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78743</v>
       </c>
-      <c r="N6" t="n">
-        <v>-0.42</v>
+      <c r="O6" t="n">
+        <v>-2.73</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1349,41 +1359,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1180</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>1.72</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="6" t="n">
         <v>9124</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-425</v>
       </c>
-      <c r="G8" t="n">
-        <v>-6321</v>
-      </c>
       <c r="H8" t="n">
+        <v>-7045</v>
+      </c>
+      <c r="I8" t="n">
         <v>39</v>
       </c>
-      <c r="I8" t="n">
-        <v>-549</v>
-      </c>
       <c r="J8" t="n">
+        <v>515</v>
+      </c>
+      <c r="K8" t="n">
         <v>179</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6082</v>
       </c>
-      <c r="L8" t="n">
-        <v>30608</v>
-      </c>
       <c r="M8" t="n">
+        <v>30551</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648673</v>
       </c>
-      <c r="N8" t="n">
-        <v>-0.17</v>
+      <c r="O8" t="n">
+        <v>0.53</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1402,41 +1417,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1815</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>1.97</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>40350</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>2919</v>
       </c>
-      <c r="G9" t="n">
-        <v>-38657</v>
-      </c>
       <c r="H9" t="n">
+        <v>-25892</v>
+      </c>
+      <c r="I9" t="n">
         <v>267</v>
       </c>
-      <c r="I9" t="n">
-        <v>6166</v>
-      </c>
       <c r="J9" t="n">
+        <v>4388</v>
+      </c>
+      <c r="K9" t="n">
         <v>335</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>22959</v>
       </c>
-      <c r="L9" t="n">
-        <v>110989</v>
-      </c>
       <c r="M9" t="n">
+        <v>113171</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482907</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.02</v>
+      <c r="O9" t="n">
+        <v>2.83</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1508,41 +1528,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>2080</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>5697</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>367</v>
       </c>
-      <c r="G11" t="n">
-        <v>-501</v>
-      </c>
       <c r="H11" t="n">
+        <v>-320</v>
+      </c>
+      <c r="I11" t="n">
         <v>152</v>
       </c>
-      <c r="I11" t="n">
-        <v>1834</v>
-      </c>
       <c r="J11" t="n">
+        <v>1376</v>
+      </c>
+      <c r="K11" t="n">
         <v>197</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2153</v>
       </c>
-      <c r="L11" t="n">
-        <v>10556</v>
-      </c>
       <c r="M11" t="n">
+        <v>10738</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89475</v>
       </c>
-      <c r="N11" t="n">
-        <v>8.84</v>
+      <c r="O11" t="n">
+        <v>17.7</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1667,41 +1692,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1850</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>1047</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="G14" t="n">
-        <v>-286</v>
-      </c>
       <c r="H14" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>-98</v>
-      </c>
       <c r="J14" t="n">
+        <v>69</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4322</v>
       </c>
-      <c r="L14" t="n">
-        <v>21737</v>
-      </c>
       <c r="M14" t="n">
+        <v>21898</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19224</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.52</v>
+      <c r="O14" t="n">
+        <v>22.56</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1720,42 +1750,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1095</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>800</v>
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="G15" t="n">
-        <v>1161</v>
-      </c>
       <c r="H15" t="n">
+        <v>919</v>
+      </c>
+      <c r="I15" t="n">
         <v>15</v>
       </c>
-      <c r="I15" t="n">
-        <v>-125</v>
-      </c>
       <c r="J15" t="n">
+        <v>-82</v>
+      </c>
+      <c r="K15" t="n">
         <v>-15</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-68</v>
       </c>
-      <c r="L15" t="n">
-        <v>-623</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-492</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1876,42 +1911,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>338.5</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="E18" t="n">
-        <v>36878</v>
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>1491</v>
       </c>
-      <c r="G18" t="n">
-        <v>1251</v>
-      </c>
       <c r="H18" t="n">
+        <v>2349</v>
+      </c>
+      <c r="I18" t="n">
         <v>163</v>
       </c>
-      <c r="I18" t="n">
-        <v>3742</v>
-      </c>
       <c r="J18" t="n">
+        <v>2985</v>
+      </c>
+      <c r="K18" t="n">
         <v>190</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>670</v>
       </c>
-      <c r="L18" t="n">
-        <v>-515</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2126,40 +2166,45 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1305</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>9.66</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>8165</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>1820</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>1543</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>459</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>742</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>295</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2450</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>12873</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140135</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>10.69</v>
       </c>
     </row>
@@ -2174,42 +2219,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-58</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L24" t="n">
         <v>-7</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-22</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2222,42 +2272,47 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F25" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G25" s="7" t="n">
         <v>1557</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1902</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-13</v>
       </c>
       <c r="J25" t="n">
         <v>-13</v>
       </c>
       <c r="K25" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L25" t="n">
         <v>-90</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-208</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2270,41 +2325,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>1030</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>6.51</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="7" t="n">
         <v>2568</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="7" t="n">
         <v>542</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-43</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-132</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K26" t="n">
         <v>64</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>898</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4680</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-106284</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.52</v>
+      <c r="O26" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="27">
@@ -2353,6 +2413,112 @@
       </c>
       <c r="N27" t="n">
         <v>7.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>4720</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>299</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12</v>
+      </c>
+      <c r="L28" t="n">
+        <v>338</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1622</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8879</v>
+      </c>
+      <c r="O28" t="n">
+        <v>18.73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>8704</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1529</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4230</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-383</v>
+      </c>
+      <c r="K29" t="n">
+        <v>32</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6178</v>
+      </c>
+      <c r="M29" t="n">
+        <v>30555</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21529</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11.85</v>
       </c>
     </row>
   </sheetData>
